--- a/experiment/Wavlet_bestx4/Test/results-Set14/Set14.xlsx
+++ b/experiment/Wavlet_bestx4/Test/results-Set14/Set14.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>23.04</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5288</v>
+        <v>0.5337</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.12</v>
+        <v>25.98</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7529</v>
+        <v>0.7502</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.42</v>
+        <v>25.45</v>
       </c>
       <c r="C4" t="n">
-        <v>0.637</v>
+        <v>0.6385</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         <v>26.34</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5799</v>
+        <v>0.5783</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.29</v>
+        <v>23.39</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7148</v>
+        <v>0.7214</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.83</v>
+        <v>32.86</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7927</v>
+        <v>0.7938</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.97</v>
+        <v>28.09</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8078</v>
+        <v>0.8113</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.55</v>
+        <v>33.69</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9173</v>
+        <v>0.9192</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.33</v>
+        <v>32.4</v>
       </c>
       <c r="C10" t="n">
-        <v>0.861</v>
+        <v>0.8632</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.28</v>
+        <v>27.35</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7469</v>
+        <v>0.7488</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.43</v>
+        <v>32.57</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9392</v>
+        <v>0.9413</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33.93</v>
+        <v>34.07</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8758</v>
+        <v>0.8779</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.18</v>
+        <v>26.29</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9347</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.22</v>
+        <v>27.07</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.7733</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.42</v>
+        <v>28.47</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7759</v>
+        <v>0.7779</v>
       </c>
     </row>
   </sheetData>
